--- a/策划文档/主线任务.xlsx
+++ b/策划文档/主线任务.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18015" windowHeight="17445"/>
+    <workbookView windowWidth="18165" windowHeight="17610" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="VIP对应开箱上限" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
   <si>
     <t>任务编号</t>
   </si>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>战力</t>
+  </si>
+  <si>
+    <t>VIP等级</t>
+  </si>
+  <si>
+    <t>开箱上限</t>
   </si>
 </sst>
 </file>
@@ -713,8 +719,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1051,1197 +1060,1197 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:9">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3">
         <v>1</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="3">
         <v>10</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="3">
         <v>9000</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:9">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3">
         <v>10</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="3">
         <v>20</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="3">
         <v>31000</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:9">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3">
         <v>20</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="3">
         <v>30</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="3">
         <v>120000</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:9">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3">
         <v>30</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="3">
         <v>40</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="3">
         <v>250000</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:9">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3">
         <v>40</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="3">
         <v>50</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="3">
         <v>550000</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3">
         <v>50</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="3">
         <v>60</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="3">
         <v>1000000</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3">
         <v>60</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="3">
         <v>70</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="3">
         <v>1700000</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:9">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3">
         <v>70</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="3">
         <v>80</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="3">
         <v>2750000</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:9">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3">
         <v>80</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="3">
         <v>90</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="3">
         <v>5200000</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:9">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3">
         <v>90</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="3">
         <v>100</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="3">
         <v>7400000</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3">
         <v>110</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="3">
         <v>8900000</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3">
         <v>120</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="3">
         <v>16000000</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3">
         <v>130</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="3">
         <v>19000000</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3">
         <v>140</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="3">
         <v>22000000</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3">
         <v>150</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="3">
         <v>25000000</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
     </row>
     <row r="18" ht="16.5" spans="1:9">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
     </row>
     <row r="19" ht="16.5" spans="1:9">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
     </row>
     <row r="20" ht="16.5" spans="1:9">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
     </row>
     <row r="21" ht="16.5" spans="1:9">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
     </row>
     <row r="22" ht="16.5" spans="1:9">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
     </row>
     <row r="23" ht="16.5" spans="1:9">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
     </row>
     <row r="24" ht="16.5" spans="1:9">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
     </row>
     <row r="25" ht="16.5" spans="1:9">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
     </row>
     <row r="26" ht="16.5" spans="1:9">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
     </row>
     <row r="27" ht="16.5" spans="1:9">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
     </row>
     <row r="28" ht="16.5" spans="1:9">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
     </row>
     <row r="29" ht="16.5" spans="1:9">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
     </row>
     <row r="30" ht="16.5" spans="1:9">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
     </row>
     <row r="31" ht="16.5" spans="1:9">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
     </row>
     <row r="32" ht="16.5" spans="1:9">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
     </row>
     <row r="33" ht="16.5" spans="1:9">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
     </row>
     <row r="34" ht="16.5" spans="1:9">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
     </row>
     <row r="35" ht="16.5" spans="1:9">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
     </row>
     <row r="36" ht="16.5" spans="1:9">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
     </row>
     <row r="37" ht="16.5" spans="1:9">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
     </row>
     <row r="38" ht="16.5" spans="1:9">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
     </row>
     <row r="39" ht="16.5" spans="1:9">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
     </row>
     <row r="40" ht="16.5" spans="1:9">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
     </row>
     <row r="41" ht="16.5" spans="1:9">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
     </row>
     <row r="42" ht="16.5" spans="1:9">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
     </row>
     <row r="43" ht="16.5" spans="1:9">
-      <c r="A43" s="2">
+      <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
     </row>
     <row r="44" ht="16.5" spans="1:9">
-      <c r="A44" s="2">
+      <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
     </row>
     <row r="45" ht="16.5" spans="1:9">
-      <c r="A45" s="2">
+      <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
     </row>
     <row r="46" ht="16.5" spans="1:9">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <v>45</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
     </row>
     <row r="47" ht="16.5" spans="1:9">
-      <c r="A47" s="2">
+      <c r="A47" s="3">
         <v>46</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
     </row>
     <row r="48" ht="16.5" spans="1:9">
-      <c r="A48" s="2">
+      <c r="A48" s="3">
         <v>47</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
     </row>
     <row r="49" ht="16.5" spans="1:9">
-      <c r="A49" s="2">
+      <c r="A49" s="3">
         <v>48</v>
       </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
     </row>
     <row r="50" ht="16.5" spans="1:9">
-      <c r="A50" s="2">
+      <c r="A50" s="3">
         <v>49</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
     </row>
     <row r="51" ht="16.5" spans="1:9">
-      <c r="A51" s="2">
+      <c r="A51" s="3">
         <v>50</v>
       </c>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
     </row>
     <row r="52" ht="16.5" spans="1:9">
-      <c r="A52" s="2">
+      <c r="A52" s="3">
         <v>51</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
     </row>
     <row r="53" ht="16.5" spans="1:9">
-      <c r="A53" s="2">
+      <c r="A53" s="3">
         <v>52</v>
       </c>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
     </row>
     <row r="54" ht="16.5" spans="1:9">
-      <c r="A54" s="2">
+      <c r="A54" s="3">
         <v>53</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
     </row>
     <row r="55" ht="16.5" spans="1:9">
-      <c r="A55" s="2">
+      <c r="A55" s="3">
         <v>54</v>
       </c>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
     </row>
     <row r="56" ht="16.5" spans="1:9">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <v>55</v>
       </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
     </row>
     <row r="57" ht="16.5" spans="1:9">
-      <c r="A57" s="2">
+      <c r="A57" s="3">
         <v>56</v>
       </c>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
     </row>
     <row r="58" ht="16.5" spans="1:9">
-      <c r="A58" s="2">
+      <c r="A58" s="3">
         <v>57</v>
       </c>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
     </row>
     <row r="59" ht="16.5" spans="1:9">
-      <c r="A59" s="2">
+      <c r="A59" s="3">
         <v>58</v>
       </c>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
     </row>
     <row r="60" ht="16.5" spans="1:9">
-      <c r="A60" s="2">
+      <c r="A60" s="3">
         <v>59</v>
       </c>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
     </row>
     <row r="61" ht="16.5" spans="1:9">
-      <c r="A61" s="2">
+      <c r="A61" s="3">
         <v>60</v>
       </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
     </row>
     <row r="62" ht="16.5" spans="1:9">
-      <c r="A62" s="2">
+      <c r="A62" s="3">
         <v>61</v>
       </c>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
     </row>
     <row r="63" ht="16.5" spans="1:9">
-      <c r="A63" s="2">
+      <c r="A63" s="3">
         <v>62</v>
       </c>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
     </row>
     <row r="64" ht="16.5" spans="1:9">
-      <c r="A64" s="2">
+      <c r="A64" s="3">
         <v>63</v>
       </c>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
     </row>
     <row r="65" ht="16.5" spans="1:9">
-      <c r="A65" s="2">
+      <c r="A65" s="3">
         <v>64</v>
       </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
     </row>
     <row r="66" ht="16.5" spans="1:9">
-      <c r="A66" s="2">
+      <c r="A66" s="3">
         <v>65</v>
       </c>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
     </row>
     <row r="67" ht="16.5" spans="1:9">
-      <c r="A67" s="2">
+      <c r="A67" s="3">
         <v>66</v>
       </c>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
     </row>
     <row r="68" ht="16.5" spans="1:9">
-      <c r="A68" s="2">
+      <c r="A68" s="3">
         <v>67</v>
       </c>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
     </row>
     <row r="69" ht="16.5" spans="1:9">
-      <c r="A69" s="2">
+      <c r="A69" s="3">
         <v>68</v>
       </c>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
     </row>
     <row r="70" ht="16.5" spans="1:9">
-      <c r="A70" s="2">
+      <c r="A70" s="3">
         <v>69</v>
       </c>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
     </row>
     <row r="71" ht="16.5" spans="1:9">
-      <c r="A71" s="2">
+      <c r="A71" s="3">
         <v>70</v>
       </c>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
     </row>
     <row r="72" ht="16.5" spans="1:9">
-      <c r="A72" s="2">
+      <c r="A72" s="3">
         <v>71</v>
       </c>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
     </row>
     <row r="73" ht="16.5" spans="1:9">
-      <c r="A73" s="2">
+      <c r="A73" s="3">
         <v>72</v>
       </c>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
     </row>
     <row r="74" ht="16.5" spans="1:9">
-      <c r="A74" s="2">
+      <c r="A74" s="3">
         <v>73</v>
       </c>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
     </row>
     <row r="75" ht="16.5" spans="1:9">
-      <c r="A75" s="2">
+      <c r="A75" s="3">
         <v>74</v>
       </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
     </row>
     <row r="76" ht="16.5" spans="1:9">
-      <c r="A76" s="2">
+      <c r="A76" s="3">
         <v>75</v>
       </c>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
     </row>
     <row r="77" ht="16.5" spans="1:9">
-      <c r="A77" s="2">
+      <c r="A77" s="3">
         <v>76</v>
       </c>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
     </row>
     <row r="78" ht="16.5" spans="1:9">
-      <c r="A78" s="2">
+      <c r="A78" s="3">
         <v>77</v>
       </c>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
     </row>
     <row r="79" ht="16.5" spans="1:9">
-      <c r="A79" s="2">
+      <c r="A79" s="3">
         <v>78</v>
       </c>
-      <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
     </row>
     <row r="80" ht="16.5" spans="1:9">
-      <c r="A80" s="2">
+      <c r="A80" s="3">
         <v>79</v>
       </c>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="3"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
     </row>
     <row r="81" ht="16.5" spans="1:9">
-      <c r="A81" s="2">
+      <c r="A81" s="3">
         <v>80</v>
       </c>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 B2:B38 B39:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"等级,杀怪,战力,开箱,强化,技能,升箱"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2254,9 +2263,149 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="2" width="11.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:2">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:2">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:2">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:2">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:2">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:2">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:2">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:2">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:2">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:2">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:2">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:2">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:2">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:2">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1700</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/策划文档/主线任务.xlsx
+++ b/策划文档/主线任务.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18165" windowHeight="17610" activeTab="1"/>
+    <workbookView windowWidth="17940" windowHeight="17535"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="63">
   <si>
     <t>任务编号</t>
   </si>
@@ -61,22 +61,157 @@
     <t>杀怪</t>
   </si>
   <si>
-    <t>开箱</t>
+    <t>称号</t>
+  </si>
+  <si>
+    <t>初入江湖</t>
+  </si>
+  <si>
+    <t>boss</t>
+  </si>
+  <si>
+    <t>强化</t>
+  </si>
+  <si>
+    <t>展露头角</t>
+  </si>
+  <si>
+    <t>战力</t>
+  </si>
+  <si>
+    <t>战力=12万</t>
+  </si>
+  <si>
+    <t>江湖少侠</t>
+  </si>
+  <si>
+    <t>技能</t>
+  </si>
+  <si>
+    <t>战力=18万</t>
+  </si>
+  <si>
+    <t>武林豪杰</t>
+  </si>
+  <si>
+    <t>战力=30万</t>
+  </si>
+  <si>
+    <t>侠骨柔情</t>
+  </si>
+  <si>
+    <t>名动江湖</t>
+  </si>
+  <si>
+    <t>战力=75万</t>
+  </si>
+  <si>
+    <t>叱诧风云</t>
   </si>
   <si>
     <t>等级</t>
   </si>
   <si>
-    <t>强化</t>
-  </si>
-  <si>
-    <t>技能</t>
-  </si>
-  <si>
-    <t>升箱</t>
-  </si>
-  <si>
-    <t>战力</t>
+    <t xml:space="preserve"> 等级*57</t>
+  </si>
+  <si>
+    <t>赤胆雄心</t>
+  </si>
+  <si>
+    <t>战力=100万</t>
+  </si>
+  <si>
+    <t>等级*65</t>
+  </si>
+  <si>
+    <t>等级*70</t>
+  </si>
+  <si>
+    <t>等级*75</t>
+  </si>
+  <si>
+    <t>战力=180万</t>
+  </si>
+  <si>
+    <t>等级*80</t>
+  </si>
+  <si>
+    <t>等级*85</t>
+  </si>
+  <si>
+    <t>战力=350万</t>
+  </si>
+  <si>
+    <t>等级*90</t>
+  </si>
+  <si>
+    <t>战力=600万</t>
+  </si>
+  <si>
+    <t>等级*100</t>
+  </si>
+  <si>
+    <t>战力=780万</t>
+  </si>
+  <si>
+    <t>等级*105</t>
+  </si>
+  <si>
+    <t>战力=850万</t>
+  </si>
+  <si>
+    <t>等级*110</t>
+  </si>
+  <si>
+    <t>战力=900万</t>
+  </si>
+  <si>
+    <t>等级*115</t>
+  </si>
+  <si>
+    <t>战力=950万</t>
+  </si>
+  <si>
+    <t>等级*120</t>
+  </si>
+  <si>
+    <t>战力=1000万</t>
+  </si>
+  <si>
+    <t>等级*125</t>
+  </si>
+  <si>
+    <t>战力=1100万</t>
+  </si>
+  <si>
+    <t>等级*130</t>
+  </si>
+  <si>
+    <t>战力=1300万</t>
+  </si>
+  <si>
+    <t>等级*135</t>
+  </si>
+  <si>
+    <t>战力=1500万</t>
+  </si>
+  <si>
+    <t>等级*140</t>
+  </si>
+  <si>
+    <t>战力=2000万</t>
+  </si>
+  <si>
+    <t>等级*145</t>
+  </si>
+  <si>
+    <t>战力=2500万</t>
+  </si>
+  <si>
+    <t>等级*150</t>
+  </si>
+  <si>
+    <t>战力=5000万</t>
   </si>
   <si>
     <t>VIP等级</t>
@@ -719,20 +854,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,6 +925,18 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -794,13 +944,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1053,1205 +1196,1425 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I81"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:K72"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="9" max="9" width="10.375"/>
+    <col min="1" max="2" width="9" style="2"/>
+    <col min="3" max="3" width="13" style="2" customWidth="1"/>
+    <col min="4" max="8" width="9" style="2"/>
+    <col min="9" max="9" width="10.375" style="2"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:9">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:9">
-      <c r="A2" s="3">
+    <row r="2" spans="1:9">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1">
         <v>1</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="1">
         <v>10</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="1">
         <v>9000</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:9">
-      <c r="A3" s="3">
+    <row r="3" spans="1:9">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3">
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1">
         <v>10</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="1">
         <v>20</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="1">
         <v>31000</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:9">
-      <c r="A4" s="3">
+    <row r="4" spans="1:9">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1">
+        <v>15</v>
+      </c>
+      <c r="H4" s="1">
+        <v>30</v>
+      </c>
+      <c r="I4" s="1">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1">
+        <v>20</v>
+      </c>
+      <c r="H5" s="1">
+        <v>40</v>
+      </c>
+      <c r="I5" s="1">
+        <v>250000</v>
+      </c>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1">
+        <v>20</v>
+      </c>
+      <c r="H6" s="1">
+        <v>50</v>
+      </c>
+      <c r="I6" s="1">
+        <v>550000</v>
+      </c>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1">
+        <v>22</v>
+      </c>
+      <c r="H7" s="1">
+        <v>60</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1">
+        <v>25</v>
+      </c>
+      <c r="H8" s="1">
+        <v>70</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1700000</v>
+      </c>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1">
+        <v>80</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2750000</v>
+      </c>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1">
+        <v>30</v>
+      </c>
+      <c r="H10" s="1">
+        <v>90</v>
+      </c>
+      <c r="I10" s="1">
+        <v>5200000</v>
+      </c>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1">
+        <v>30</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="1">
+        <v>7400000</v>
+      </c>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3">
+      <c r="B12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1">
+        <v>32</v>
+      </c>
+      <c r="H12" s="1">
+        <v>110</v>
+      </c>
+      <c r="I12" s="1">
+        <v>8900000</v>
+      </c>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1">
+        <v>33</v>
+      </c>
+      <c r="H13" s="1">
+        <v>120</v>
+      </c>
+      <c r="I13" s="1">
+        <v>16000000</v>
+      </c>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1">
+        <v>33</v>
+      </c>
+      <c r="H14" s="1">
+        <v>130</v>
+      </c>
+      <c r="I14" s="1">
+        <v>19000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1">
+        <v>35</v>
+      </c>
+      <c r="H15" s="1">
+        <v>140</v>
+      </c>
+      <c r="I15" s="1">
+        <v>22000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1">
+        <v>35</v>
+      </c>
+      <c r="H16" s="1">
+        <v>150</v>
+      </c>
+      <c r="I16" s="1">
+        <v>25000000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1">
+        <v>37</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="3">
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1">
+        <v>38</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1">
+        <v>40</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1">
+        <v>42</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1">
+        <v>43</v>
+      </c>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1">
+        <v>45</v>
+      </c>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1">
+        <v>47</v>
+      </c>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1">
+        <v>48</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1">
+        <v>49</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1">
+        <v>50</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1">
+        <v>52</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1">
+        <v>53</v>
+      </c>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1">
+        <v>54</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1">
+        <v>55</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="I4" s="3">
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:9">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="B31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1">
+        <v>56</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1">
+        <v>57</v>
+      </c>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1">
+        <v>58</v>
+      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3">
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1">
+        <v>59</v>
+      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1">
+        <v>60</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1">
+        <v>61</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1">
+        <v>62</v>
+      </c>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="3">
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1">
+        <v>65</v>
+      </c>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1">
+        <v>67</v>
+      </c>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1">
+        <v>70</v>
+      </c>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="I5" s="3">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:9">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="B41" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3">
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1">
+        <v>71</v>
+      </c>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1">
+        <v>75</v>
+      </c>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1">
+        <v>76</v>
+      </c>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1">
+        <v>80</v>
+      </c>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1">
+        <v>72</v>
+      </c>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1">
+        <v>85</v>
+      </c>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1">
+        <v>87</v>
+      </c>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1">
+        <v>89</v>
+      </c>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1">
+        <v>90</v>
+      </c>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1">
+        <v>95</v>
+      </c>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1">
+        <v>100</v>
+      </c>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="3">
-        <v>50</v>
-      </c>
-      <c r="I6" s="3">
-        <v>550000</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:9">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3">
-        <v>50</v>
-      </c>
-      <c r="H7" s="3">
-        <v>60</v>
-      </c>
-      <c r="I7" s="3">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:9">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3">
-        <v>60</v>
-      </c>
-      <c r="H8" s="3">
-        <v>70</v>
-      </c>
-      <c r="I8" s="3">
-        <v>1700000</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:9">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3">
-        <v>70</v>
-      </c>
-      <c r="H9" s="3">
-        <v>80</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2750000</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:9">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3">
-        <v>80</v>
-      </c>
-      <c r="H10" s="3">
-        <v>90</v>
-      </c>
-      <c r="I10" s="3">
-        <v>5200000</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:9">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3">
-        <v>90</v>
-      </c>
-      <c r="H11" s="3">
-        <v>100</v>
-      </c>
-      <c r="I11" s="3">
-        <v>7400000</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:9">
-      <c r="A12" s="3">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1">
+        <v>102</v>
+      </c>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1">
+        <v>105</v>
+      </c>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3">
+      <c r="C54" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1">
+        <v>107</v>
+      </c>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1">
         <v>110</v>
       </c>
-      <c r="I12" s="3">
-        <v>8900000</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:9">
-      <c r="A13" s="3">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3">
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1">
+        <v>112</v>
+      </c>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1">
+        <v>115</v>
+      </c>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1">
+        <v>117</v>
+      </c>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1">
         <v>120</v>
       </c>
-      <c r="I13" s="3">
-        <v>16000000</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:9">
-      <c r="A14" s="3">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3">
-        <v>130</v>
-      </c>
-      <c r="I14" s="3">
-        <v>19000000</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:9">
-      <c r="A15" s="3">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3">
-        <v>140</v>
-      </c>
-      <c r="I15" s="3">
-        <v>22000000</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:9">
-      <c r="A16" s="3">
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3">
-        <v>150</v>
-      </c>
-      <c r="I16" s="3">
-        <v>25000000</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:9">
-      <c r="A17" s="3">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-    </row>
-    <row r="18" ht="16.5" spans="1:9">
-      <c r="A18" s="3">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:9">
-      <c r="A19" s="3">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:9">
-      <c r="A20" s="3">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-    </row>
-    <row r="21" ht="16.5" spans="1:9">
-      <c r="A21" s="3">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-    </row>
-    <row r="22" ht="16.5" spans="1:9">
-      <c r="A22" s="3">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-    </row>
-    <row r="23" ht="16.5" spans="1:9">
-      <c r="A23" s="3">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:9">
-      <c r="A24" s="3">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-    </row>
-    <row r="25" ht="16.5" spans="1:9">
-      <c r="A25" s="3">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:9">
-      <c r="A26" s="3">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-    </row>
-    <row r="27" ht="16.5" spans="1:9">
-      <c r="A27" s="3">
-        <v>26</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-    </row>
-    <row r="28" ht="16.5" spans="1:9">
-      <c r="A28" s="3">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-    </row>
-    <row r="29" ht="16.5" spans="1:9">
-      <c r="A29" s="3">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-    </row>
-    <row r="30" ht="16.5" spans="1:9">
-      <c r="A30" s="3">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-    </row>
-    <row r="31" ht="16.5" spans="1:9">
-      <c r="A31" s="3">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:9">
-      <c r="A32" s="3">
-        <v>31</v>
-      </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:9">
-      <c r="A33" s="3">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-    </row>
-    <row r="34" ht="16.5" spans="1:9">
-      <c r="A34" s="3">
-        <v>33</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-    </row>
-    <row r="35" ht="16.5" spans="1:9">
-      <c r="A35" s="3">
-        <v>34</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-    </row>
-    <row r="36" ht="16.5" spans="1:9">
-      <c r="A36" s="3">
-        <v>35</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-    </row>
-    <row r="37" ht="16.5" spans="1:9">
-      <c r="A37" s="3">
-        <v>36</v>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-    </row>
-    <row r="38" ht="16.5" spans="1:9">
-      <c r="A38" s="3">
-        <v>37</v>
-      </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-    </row>
-    <row r="39" ht="16.5" spans="1:9">
-      <c r="A39" s="3">
-        <v>38</v>
-      </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-    </row>
-    <row r="40" ht="16.5" spans="1:9">
-      <c r="A40" s="3">
-        <v>39</v>
-      </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-    </row>
-    <row r="41" ht="16.5" spans="1:9">
-      <c r="A41" s="3">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-    </row>
-    <row r="42" ht="16.5" spans="1:9">
-      <c r="A42" s="3">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-    </row>
-    <row r="43" ht="16.5" spans="1:9">
-      <c r="A43" s="3">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-    </row>
-    <row r="44" ht="16.5" spans="1:9">
-      <c r="A44" s="3">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-    </row>
-    <row r="45" ht="16.5" spans="1:9">
-      <c r="A45" s="3">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-    </row>
-    <row r="46" ht="16.5" spans="1:9">
-      <c r="A46" s="3">
-        <v>45</v>
-      </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-    </row>
-    <row r="47" ht="16.5" spans="1:9">
-      <c r="A47" s="3">
-        <v>46</v>
-      </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-    </row>
-    <row r="48" ht="16.5" spans="1:9">
-      <c r="A48" s="3">
-        <v>47</v>
-      </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-    </row>
-    <row r="49" ht="16.5" spans="1:9">
-      <c r="A49" s="3">
+      <c r="C60" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-    </row>
-    <row r="50" ht="16.5" spans="1:9">
-      <c r="A50" s="3">
-        <v>49</v>
-      </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-    </row>
-    <row r="51" ht="16.5" spans="1:9">
-      <c r="A51" s="3">
-        <v>50</v>
-      </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-    </row>
-    <row r="52" ht="16.5" spans="1:9">
-      <c r="A52" s="3">
-        <v>51</v>
-      </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-    </row>
-    <row r="53" ht="16.5" spans="1:9">
-      <c r="A53" s="3">
-        <v>52</v>
-      </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-    </row>
-    <row r="54" ht="16.5" spans="1:9">
-      <c r="A54" s="3">
-        <v>53</v>
-      </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-    </row>
-    <row r="55" ht="16.5" spans="1:9">
-      <c r="A55" s="3">
-        <v>54</v>
-      </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-    </row>
-    <row r="56" ht="16.5" spans="1:9">
-      <c r="A56" s="3">
-        <v>55</v>
-      </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-    </row>
-    <row r="57" ht="16.5" spans="1:9">
-      <c r="A57" s="3">
-        <v>56</v>
-      </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-    </row>
-    <row r="58" ht="16.5" spans="1:9">
-      <c r="A58" s="3">
-        <v>57</v>
-      </c>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
-    </row>
-    <row r="59" ht="16.5" spans="1:9">
-      <c r="A59" s="3">
-        <v>58</v>
-      </c>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-    </row>
-    <row r="60" ht="16.5" spans="1:9">
-      <c r="A60" s="3">
-        <v>59</v>
-      </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
+      <c r="G60" s="4">
+        <v>122</v>
+      </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
     </row>
-    <row r="61" ht="16.5" spans="1:9">
-      <c r="A61" s="3">
+    <row r="61" spans="1:9">
+      <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
+      <c r="B61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
+      <c r="G61" s="4">
+        <v>125</v>
+      </c>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
     </row>
-    <row r="62" ht="16.5" spans="1:9">
-      <c r="A62" s="3">
+    <row r="62" spans="1:9">
+      <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
+      <c r="B62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
+      <c r="G62" s="4">
+        <v>127</v>
+      </c>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
     </row>
-    <row r="63" ht="16.5" spans="1:9">
-      <c r="A63" s="3">
+    <row r="63" spans="1:9">
+      <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
+      <c r="B63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
+      <c r="G63" s="4">
+        <v>130</v>
+      </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
     </row>
-    <row r="64" ht="16.5" spans="1:9">
-      <c r="A64" s="3">
+    <row r="64" spans="1:9">
+      <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
+      <c r="B64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
+      <c r="G64" s="4">
+        <v>132</v>
+      </c>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
     </row>
-    <row r="65" ht="16.5" spans="1:9">
-      <c r="A65" s="3">
+    <row r="65" spans="1:9">
+      <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
+      <c r="B65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
+      <c r="G65" s="4">
+        <v>135</v>
+      </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
     </row>
-    <row r="66" ht="16.5" spans="1:9">
-      <c r="A66" s="3">
+    <row r="66" spans="1:9">
+      <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
+      <c r="B66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
+      <c r="G66" s="4">
+        <v>137</v>
+      </c>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
     </row>
-    <row r="67" ht="16.5" spans="1:9">
-      <c r="A67" s="3">
+    <row r="67" spans="1:9">
+      <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
+      <c r="B67" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
+      <c r="G67" s="4">
+        <v>140</v>
+      </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
     </row>
-    <row r="68" ht="16.5" spans="1:9">
-      <c r="A68" s="3">
+    <row r="68" spans="1:9">
+      <c r="A68" s="1">
         <v>67</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
+      <c r="B68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
+      <c r="G68" s="4">
+        <v>142</v>
+      </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
     </row>
-    <row r="69" ht="16.5" spans="1:9">
-      <c r="A69" s="3">
+    <row r="69" spans="1:9">
+      <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
+      <c r="B69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
+      <c r="G69" s="4">
+        <v>145</v>
+      </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
     </row>
-    <row r="70" ht="16.5" spans="1:9">
-      <c r="A70" s="3">
+    <row r="70" spans="1:9">
+      <c r="A70" s="1">
         <v>69</v>
       </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
+      <c r="B70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
+      <c r="G70" s="4">
+        <v>147</v>
+      </c>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
     </row>
-    <row r="71" ht="16.5" spans="1:9">
-      <c r="A71" s="3">
+    <row r="71" spans="1:9">
+      <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
+      <c r="B71" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
+      <c r="G71" s="4">
+        <v>150</v>
+      </c>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
     </row>
-    <row r="72" ht="16.5" spans="1:9">
-      <c r="A72" s="3">
+    <row r="72" spans="1:9">
+      <c r="A72" s="1">
         <v>71</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
+      <c r="B72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
+      <c r="G72" s="4">
+        <v>150</v>
+      </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
     </row>
-    <row r="73" ht="16.5" spans="1:9">
-      <c r="A73" s="3">
-        <v>72</v>
-      </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-    </row>
-    <row r="74" ht="16.5" spans="1:9">
-      <c r="A74" s="3">
-        <v>73</v>
-      </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-    </row>
-    <row r="75" ht="16.5" spans="1:9">
-      <c r="A75" s="3">
-        <v>74</v>
-      </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
-    </row>
-    <row r="76" ht="16.5" spans="1:9">
-      <c r="A76" s="3">
-        <v>75</v>
-      </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-    </row>
-    <row r="77" ht="16.5" spans="1:9">
-      <c r="A77" s="3">
-        <v>76</v>
-      </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-    </row>
-    <row r="78" ht="16.5" spans="1:9">
-      <c r="A78" s="3">
-        <v>77</v>
-      </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-    </row>
-    <row r="79" ht="16.5" spans="1:9">
-      <c r="A79" s="3">
-        <v>78</v>
-      </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-    </row>
-    <row r="80" ht="16.5" spans="1:9">
-      <c r="A80" s="3">
-        <v>79</v>
-      </c>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-    </row>
-    <row r="81" ht="16.5" spans="1:9">
-      <c r="A81" s="3">
-        <v>80</v>
-      </c>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="between" text="称号">
+      <formula>NOT(ISERROR(SEARCH("称号",B13)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B$1:B$1048576">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="between" text="称号">
+      <formula>NOT(ISERROR(SEARCH("称号",B1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
-      <formula1>"等级,杀怪,战力,开箱,强化,技能,升箱"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B72 B73:B1048576">
+      <formula1>"等级,杀怪,战力,称号,强化,技能,升箱,boss"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2271,137 +2634,137 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:2">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>200</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:2">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>300</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:2">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>400</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:2">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>600</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>700</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>800</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>900</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>1000</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>1100</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>1200</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>1300</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>1400</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>1500</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>1600</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>1700</v>
       </c>
     </row>

--- a/策划文档/主线任务.xlsx
+++ b/策划文档/主线任务.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17940" windowHeight="17535"/>
+    <workbookView windowWidth="18825" windowHeight="17535"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="117">
   <si>
     <t>任务编号</t>
   </si>
@@ -61,21 +61,60 @@
     <t>杀怪</t>
   </si>
   <si>
+    <t>em000(37,41)</t>
+  </si>
+  <si>
+    <t>dingpamao*3</t>
+  </si>
+  <si>
+    <t>绑元*10000</t>
+  </si>
+  <si>
     <t>称号</t>
   </si>
   <si>
     <t>初入江湖</t>
   </si>
   <si>
+    <t>强化石*100</t>
+  </si>
+  <si>
+    <t>fmg(246,105)</t>
+  </si>
+  <si>
+    <t>huangshayi*5</t>
+  </si>
+  <si>
     <t>boss</t>
   </si>
   <si>
+    <t>首领</t>
+  </si>
+  <si>
     <t>强化</t>
   </si>
   <si>
+    <t>强化到3级</t>
+  </si>
+  <si>
+    <t>fmg(252,93)</t>
+  </si>
+  <si>
+    <t>baishayi*8</t>
+  </si>
+  <si>
+    <t>绑元*50000</t>
+  </si>
+  <si>
     <t>展露头角</t>
   </si>
   <si>
+    <t>xbsd(50,50)</t>
+  </si>
+  <si>
+    <t>qianchong*10</t>
+  </si>
+  <si>
     <t>战力</t>
   </si>
   <si>
@@ -85,6 +124,12 @@
     <t>江湖少侠</t>
   </si>
   <si>
+    <t>rxsc800(50,50)</t>
+  </si>
+  <si>
+    <t>duxie*15</t>
+  </si>
+  <si>
     <t>技能</t>
   </si>
   <si>
@@ -94,6 +139,15 @@
     <t>武林豪杰</t>
   </si>
   <si>
+    <t>zlgm(50,50)</t>
+  </si>
+  <si>
+    <t>womashouwei*15</t>
+  </si>
+  <si>
+    <t>绑元*20000</t>
+  </si>
+  <si>
     <t>战力=30万</t>
   </si>
   <si>
@@ -103,21 +157,42 @@
     <t>名动江湖</t>
   </si>
   <si>
+    <t>强化石*500</t>
+  </si>
+  <si>
+    <t>swdt001(50,50)</t>
+  </si>
+  <si>
+    <t>baiyezhu*15</t>
+  </si>
+  <si>
     <t>战力=75万</t>
   </si>
   <si>
     <t>叱诧风云</t>
   </si>
   <si>
+    <t>zzdt001(50，50)</t>
+  </si>
+  <si>
+    <t>womashouwei*25</t>
+  </si>
+  <si>
     <t>等级</t>
   </si>
   <si>
-    <t xml:space="preserve"> 等级*57</t>
+    <t>等级*57</t>
   </si>
   <si>
     <t>赤胆雄心</t>
   </si>
   <si>
+    <t>rxsc016（40，40）</t>
+  </si>
+  <si>
+    <t>womajiaozhu*15</t>
+  </si>
+  <si>
     <t>战力=100万</t>
   </si>
   <si>
@@ -212,6 +287,93 @@
   </si>
   <si>
     <t>战力=5000万</t>
+  </si>
+  <si>
+    <t>等级*151</t>
+  </si>
+  <si>
+    <t>战力=6000万</t>
+  </si>
+  <si>
+    <t>等级*152</t>
+  </si>
+  <si>
+    <t>战力=7000万</t>
+  </si>
+  <si>
+    <t>等级*153</t>
+  </si>
+  <si>
+    <t>战力=8000万</t>
+  </si>
+  <si>
+    <t>等级*154</t>
+  </si>
+  <si>
+    <t>战力=9000万</t>
+  </si>
+  <si>
+    <t>等级*155</t>
+  </si>
+  <si>
+    <t>战力=1亿</t>
+  </si>
+  <si>
+    <t>等级*156</t>
+  </si>
+  <si>
+    <t>战力=1.1亿</t>
+  </si>
+  <si>
+    <t>等级*157</t>
+  </si>
+  <si>
+    <t>战力=1.2亿</t>
+  </si>
+  <si>
+    <t>等级*158</t>
+  </si>
+  <si>
+    <t>战力=1.3亿</t>
+  </si>
+  <si>
+    <t>等级*159</t>
+  </si>
+  <si>
+    <t>战力=1.4亿</t>
+  </si>
+  <si>
+    <t>等级*160</t>
+  </si>
+  <si>
+    <t>战力=1.5亿</t>
+  </si>
+  <si>
+    <t>等级*161</t>
+  </si>
+  <si>
+    <t>战力=1.6亿</t>
+  </si>
+  <si>
+    <t>等级*162</t>
+  </si>
+  <si>
+    <t>战力=1.7亿</t>
+  </si>
+  <si>
+    <t>等级*163</t>
+  </si>
+  <si>
+    <t>战力=1.8亿</t>
+  </si>
+  <si>
+    <t>等级*164</t>
+  </si>
+  <si>
+    <t>战力=1.9亿</t>
+  </si>
+  <si>
+    <t>等级*165</t>
   </si>
   <si>
     <t>VIP等级</t>
@@ -389,12 +551,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -730,7 +898,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -754,16 +922,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -772,89 +940,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -864,13 +1032,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1196,13 +1373,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="13" style="2" customWidth="1"/>
-    <col min="4" max="8" width="9" style="2"/>
-    <col min="9" max="9" width="10.375" style="2"/>
+    <col min="3" max="3" width="14.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="18.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.875" style="2" customWidth="1"/>
+    <col min="7" max="8" width="9" style="2"/>
+    <col min="9" max="9" width="11.625" style="2"/>
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1216,7 +1396,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1243,9 +1423,15 @@
         <v>9</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="D2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="G2" s="1">
         <v>1</v>
       </c>
@@ -1261,14 +1447,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="G3" s="1">
         <v>10</v>
       </c>
@@ -1287,9 +1475,15 @@
         <v>9</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="D4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="G4" s="1">
         <v>15</v>
       </c>
@@ -1305,12 +1499,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="G5" s="1">
         <v>20</v>
       </c>
@@ -1327,11 +1525,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1">
         <v>20</v>
@@ -1352,9 +1552,15 @@
         <v>9</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="G7" s="1">
         <v>22</v>
       </c>
@@ -1371,14 +1577,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="4"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="G8" s="1">
         <v>25</v>
       </c>
@@ -1398,9 +1606,15 @@
         <v>9</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="D9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="G9" s="1">
         <v>25</v>
       </c>
@@ -1417,12 +1631,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="D10" s="4"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="G10" s="1">
         <v>30</v>
       </c>
@@ -1439,14 +1655,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
       <c r="G11" s="1">
         <v>30</v>
       </c>
@@ -1463,12 +1681,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="D12" s="4"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="G12" s="1">
         <v>32</v>
       </c>
@@ -1485,14 +1705,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="4"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="G13" s="1">
         <v>33</v>
       </c>
@@ -1512,9 +1734,15 @@
         <v>9</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="D14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="G14" s="1">
         <v>33</v>
       </c>
@@ -1530,12 +1758,14 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="D15" s="4"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="G15" s="1">
         <v>35</v>
       </c>
@@ -1551,14 +1781,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="D16" s="4"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="G16" s="1">
         <v>35</v>
       </c>
@@ -1574,12 +1806,14 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="D17" s="4"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="G17" s="1">
         <v>37</v>
       </c>
@@ -1591,14 +1825,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="4"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+      <c r="F18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="G18" s="1">
         <v>38</v>
       </c>
@@ -1613,26 +1849,36 @@
         <v>9</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+      <c r="D19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="G19" s="1">
         <v>40</v>
       </c>
       <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+      <c r="I19" s="1">
+        <v>250000</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
+      <c r="D20" s="4"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+      <c r="F20" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="G20" s="1">
         <v>42</v>
       </c>
@@ -1644,14 +1890,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="D21" s="4"/>
       <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
+      <c r="F21" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="G21" s="1">
         <v>43</v>
       </c>
@@ -1663,14 +1911,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="4"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+      <c r="F22" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="G22" s="1">
         <v>45</v>
       </c>
@@ -1685,9 +1935,15 @@
         <v>9</v>
       </c>
       <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+      <c r="D23" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="G23" s="1">
         <v>47</v>
       </c>
@@ -1699,12 +1955,14 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
+      <c r="D24" s="4"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="F24" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="G24" s="1">
         <v>48</v>
       </c>
@@ -1716,14 +1974,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="4"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+      <c r="F25" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G25" s="1">
         <v>49</v>
       </c>
@@ -1738,26 +1998,36 @@
         <v>9</v>
       </c>
       <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="D26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="G26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+      <c r="I26" s="1">
+        <v>550000</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
+      <c r="D27" s="4"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
+      <c r="F27" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="G27" s="1">
         <v>52</v>
       </c>
@@ -1769,14 +2039,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="D28" s="4"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
+      <c r="F28" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="G28" s="1">
         <v>53</v>
       </c>
@@ -1788,14 +2060,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="4"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
+      <c r="F29" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G29" s="1">
         <v>54</v>
       </c>
@@ -1810,9 +2084,15 @@
         <v>9</v>
       </c>
       <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
+      <c r="D30" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="G30" s="1">
         <v>55</v>
       </c>
@@ -1824,12 +2104,14 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="D31" s="4"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
+      <c r="F31" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="G31" s="1">
         <v>56</v>
       </c>
@@ -1841,14 +2123,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D32" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="D32" s="4"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
+      <c r="F32" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="G32" s="1">
         <v>57</v>
       </c>
@@ -1860,14 +2144,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="4"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
+      <c r="F33" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G33" s="1">
         <v>58</v>
       </c>
@@ -1882,9 +2168,15 @@
         <v>9</v>
       </c>
       <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
+      <c r="D34" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="G34" s="1">
         <v>59</v>
       </c>
@@ -1896,31 +2188,37 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
+      <c r="D35" s="4"/>
       <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
+      <c r="F35" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G35" s="1">
         <v>60</v>
       </c>
       <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+      <c r="I35" s="1">
+        <v>1000000</v>
+      </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="D36" s="4"/>
       <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
+      <c r="F36" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G36" s="1">
         <v>61</v>
       </c>
@@ -1932,12 +2230,14 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
+      <c r="D37" s="4"/>
       <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
+      <c r="F37" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G37" s="1">
         <v>62</v>
       </c>
@@ -1949,14 +2249,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="D38" s="4"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
+      <c r="F38" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G38" s="1">
         <v>65</v>
       </c>
@@ -1968,12 +2270,14 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
+      <c r="D39" s="4"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
+      <c r="F39" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G39" s="1">
         <v>67</v>
       </c>
@@ -1985,31 +2289,37 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D40" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="D40" s="4"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
+      <c r="F40" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G40" s="1">
         <v>70</v>
       </c>
       <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
+      <c r="I40" s="1">
+        <v>1700000</v>
+      </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="1">
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
+      <c r="D41" s="4"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
+      <c r="F41" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G41" s="1">
         <v>71</v>
       </c>
@@ -2021,14 +2331,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="D42" s="4"/>
       <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
+      <c r="F42" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G42" s="1">
         <v>75</v>
       </c>
@@ -2040,14 +2352,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D43" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="D43" s="4"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
+      <c r="F43" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G43" s="1">
         <v>76</v>
       </c>
@@ -2059,33 +2373,39 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" s="1"/>
+        <v>59</v>
+      </c>
+      <c r="D44" s="4"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
+      <c r="F44" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G44" s="1">
         <v>80</v>
       </c>
       <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
+      <c r="I44" s="1">
+        <v>2750000</v>
+      </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="1">
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
+      <c r="D45" s="4"/>
       <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G45" s="1">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -2095,14 +2415,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D46" s="1"/>
+        <v>60</v>
+      </c>
+      <c r="D46" s="4"/>
       <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
+      <c r="F46" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G46" s="1">
         <v>85</v>
       </c>
@@ -2114,14 +2436,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D47" s="1"/>
+        <v>61</v>
+      </c>
+      <c r="D47" s="4"/>
       <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
+      <c r="F47" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G47" s="1">
         <v>87</v>
       </c>
@@ -2133,12 +2457,14 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
+      <c r="D48" s="4"/>
       <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
+      <c r="F48" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G48" s="1">
         <v>89</v>
       </c>
@@ -2150,33 +2476,39 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D49" s="1"/>
+        <v>62</v>
+      </c>
+      <c r="D49" s="4"/>
       <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
+      <c r="F49" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G49" s="1">
         <v>90</v>
       </c>
       <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
+      <c r="I49" s="1">
+        <v>5200000</v>
+      </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="1">
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D50" s="1"/>
+        <v>63</v>
+      </c>
+      <c r="D50" s="4"/>
       <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
+      <c r="F50" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G50" s="1">
         <v>95</v>
       </c>
@@ -2188,33 +2520,39 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D51" s="1"/>
+        <v>64</v>
+      </c>
+      <c r="D51" s="4"/>
       <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
+      <c r="F51" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G51" s="1">
         <v>100</v>
       </c>
       <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="I51" s="1">
+        <v>7400000</v>
+      </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="1">
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D52" s="1"/>
+        <v>65</v>
+      </c>
+      <c r="D52" s="4"/>
       <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
+      <c r="F52" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G52" s="1">
         <v>102</v>
       </c>
@@ -2226,14 +2564,16 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D53" s="1"/>
+        <v>66</v>
+      </c>
+      <c r="D53" s="4"/>
       <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
+      <c r="F53" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G53" s="1">
         <v>105</v>
       </c>
@@ -2245,14 +2585,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D54" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="D54" s="4"/>
       <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
+      <c r="F54" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G54" s="1">
         <v>107</v>
       </c>
@@ -2264,33 +2606,39 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D55" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="D55" s="4"/>
       <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
+      <c r="F55" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G55" s="1">
         <v>110</v>
       </c>
       <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
+      <c r="I55" s="1">
+        <v>8900000</v>
+      </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="1">
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D56" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="D56" s="4"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
+      <c r="F56" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G56" s="1">
         <v>112</v>
       </c>
@@ -2302,14 +2650,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D57" s="1"/>
+        <v>70</v>
+      </c>
+      <c r="D57" s="4"/>
       <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
+      <c r="F57" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G57" s="1">
         <v>115</v>
       </c>
@@ -2321,14 +2671,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D58" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="D58" s="4"/>
       <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
+      <c r="F58" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G58" s="1">
         <v>117</v>
       </c>
@@ -2340,266 +2692,1027 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D59" s="1"/>
+        <v>72</v>
+      </c>
+      <c r="D59" s="4"/>
       <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
+      <c r="F59" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G59" s="1">
         <v>120</v>
       </c>
       <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
+      <c r="I59" s="1">
+        <v>16000000</v>
+      </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="1">
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>48</v>
+        <v>28</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4">
+      <c r="E60" s="1"/>
+      <c r="F60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G60" s="1">
         <v>122</v>
       </c>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C61" s="4" t="s">
         <v>49</v>
       </c>
+      <c r="C61" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4">
+      <c r="E61" s="1"/>
+      <c r="F61" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G61" s="1">
         <v>125</v>
       </c>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="1">
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>50</v>
+        <v>28</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4">
+      <c r="E62" s="1"/>
+      <c r="F62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" s="1">
         <v>127</v>
       </c>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="1">
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4">
+      <c r="E63" s="1"/>
+      <c r="F63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G63" s="1">
         <v>130</v>
       </c>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1">
+        <v>19000000</v>
+      </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="1">
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>52</v>
+        <v>28</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4">
+      <c r="E64" s="1"/>
+      <c r="F64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G64" s="1">
         <v>132</v>
       </c>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="1">
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4">
+      <c r="E65" s="1"/>
+      <c r="F65" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G65" s="1">
         <v>135</v>
       </c>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="1">
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>54</v>
+        <v>28</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4">
+      <c r="E66" s="1"/>
+      <c r="F66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G66" s="1">
         <v>137</v>
       </c>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="1">
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4">
+      <c r="E67" s="1"/>
+      <c r="F67" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67" s="1">
         <v>140</v>
       </c>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1">
+        <v>22000000</v>
+      </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="1">
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4">
+      <c r="E68" s="1"/>
+      <c r="F68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G68" s="1">
         <v>142</v>
       </c>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="1">
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>57</v>
+        <v>49</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4">
+      <c r="E69" s="1"/>
+      <c r="F69" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G69" s="1">
         <v>145</v>
       </c>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="1">
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>58</v>
+        <v>28</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4">
+      <c r="E70" s="1"/>
+      <c r="F70" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G70" s="1">
         <v>147</v>
       </c>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="1">
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>59</v>
+        <v>49</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4">
+      <c r="E71" s="1"/>
+      <c r="F71" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G71" s="1">
         <v>150</v>
       </c>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1">
+        <v>25000000</v>
+      </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="1">
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>60</v>
+        <v>28</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4">
+      <c r="E72" s="1"/>
+      <c r="F72" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G72" s="1">
         <v>150</v>
       </c>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1">
+        <v>25000000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D73" s="8"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G73" s="7">
+        <v>151</v>
+      </c>
+      <c r="H73" s="7"/>
+      <c r="I73" s="7">
+        <f>I71+5000000</f>
+        <v>30000000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D74" s="8"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G74" s="7">
+        <v>151</v>
+      </c>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7">
+        <f t="shared" ref="I74:I101" si="0">I72+5000000</f>
+        <v>30000000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D75" s="8"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G75" s="7">
+        <f>G73+1</f>
+        <v>152</v>
+      </c>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7">
+        <f t="shared" si="0"/>
+        <v>35000000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D76" s="8"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G76" s="7">
+        <f t="shared" ref="G76:G101" si="1">G74+1</f>
+        <v>152</v>
+      </c>
+      <c r="H76" s="7"/>
+      <c r="I76" s="7">
+        <f t="shared" si="0"/>
+        <v>35000000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D77" s="8"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G77" s="7">
+        <f t="shared" si="1"/>
+        <v>153</v>
+      </c>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7">
+        <f t="shared" si="0"/>
+        <v>40000000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D78" s="8"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G78" s="7">
+        <f t="shared" si="1"/>
+        <v>153</v>
+      </c>
+      <c r="H78" s="7"/>
+      <c r="I78" s="7">
+        <f t="shared" si="0"/>
+        <v>40000000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D79" s="8"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G79" s="7">
+        <f t="shared" si="1"/>
+        <v>154</v>
+      </c>
+      <c r="H79" s="7"/>
+      <c r="I79" s="7">
+        <f t="shared" si="0"/>
+        <v>45000000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D80" s="8"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G80" s="7">
+        <f t="shared" si="1"/>
+        <v>154</v>
+      </c>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7">
+        <f t="shared" si="0"/>
+        <v>45000000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D81" s="8"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G81" s="7">
+        <f t="shared" si="1"/>
+        <v>155</v>
+      </c>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7">
+        <f t="shared" si="0"/>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D82" s="8"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G82" s="7">
+        <f t="shared" si="1"/>
+        <v>155</v>
+      </c>
+      <c r="H82" s="7"/>
+      <c r="I82" s="7">
+        <f t="shared" si="0"/>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D83" s="8"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G83" s="7">
+        <f t="shared" si="1"/>
+        <v>156</v>
+      </c>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7">
+        <f t="shared" si="0"/>
+        <v>55000000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D84" s="8"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G84" s="7">
+        <f t="shared" si="1"/>
+        <v>156</v>
+      </c>
+      <c r="H84" s="7"/>
+      <c r="I84" s="7">
+        <f t="shared" si="0"/>
+        <v>55000000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D85" s="8"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G85" s="7">
+        <f t="shared" si="1"/>
+        <v>157</v>
+      </c>
+      <c r="H85" s="7"/>
+      <c r="I85" s="7">
+        <f t="shared" si="0"/>
+        <v>60000000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D86" s="8"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G86" s="7">
+        <f t="shared" si="1"/>
+        <v>157</v>
+      </c>
+      <c r="H86" s="7"/>
+      <c r="I86" s="7">
+        <f t="shared" si="0"/>
+        <v>60000000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D87" s="8"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G87" s="7">
+        <f t="shared" si="1"/>
+        <v>158</v>
+      </c>
+      <c r="H87" s="7"/>
+      <c r="I87" s="7">
+        <f t="shared" si="0"/>
+        <v>65000000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D88" s="8"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G88" s="7">
+        <f t="shared" si="1"/>
+        <v>158</v>
+      </c>
+      <c r="H88" s="7"/>
+      <c r="I88" s="7">
+        <f t="shared" si="0"/>
+        <v>65000000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D89" s="8"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G89" s="7">
+        <f t="shared" si="1"/>
+        <v>159</v>
+      </c>
+      <c r="H89" s="7"/>
+      <c r="I89" s="7">
+        <f t="shared" si="0"/>
+        <v>70000000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D90" s="8"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G90" s="7">
+        <f t="shared" si="1"/>
+        <v>159</v>
+      </c>
+      <c r="H90" s="7"/>
+      <c r="I90" s="7">
+        <f t="shared" si="0"/>
+        <v>70000000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D91" s="8"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G91" s="7">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="H91" s="7"/>
+      <c r="I91" s="7">
+        <f t="shared" si="0"/>
+        <v>75000000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D92" s="8"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G92" s="7">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="H92" s="7"/>
+      <c r="I92" s="7">
+        <f t="shared" si="0"/>
+        <v>75000000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D93" s="8"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G93" s="7">
+        <f t="shared" si="1"/>
+        <v>161</v>
+      </c>
+      <c r="H93" s="7"/>
+      <c r="I93" s="7">
+        <f t="shared" si="0"/>
+        <v>80000000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D94" s="8"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G94" s="7">
+        <f t="shared" si="1"/>
+        <v>161</v>
+      </c>
+      <c r="H94" s="7"/>
+      <c r="I94" s="7">
+        <f t="shared" si="0"/>
+        <v>80000000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D95" s="8"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G95" s="7">
+        <f t="shared" si="1"/>
+        <v>162</v>
+      </c>
+      <c r="H95" s="7"/>
+      <c r="I95" s="7">
+        <f t="shared" si="0"/>
+        <v>85000000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D96" s="8"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G96" s="7">
+        <f t="shared" si="1"/>
+        <v>162</v>
+      </c>
+      <c r="H96" s="7"/>
+      <c r="I96" s="7">
+        <f t="shared" si="0"/>
+        <v>85000000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D97" s="8"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G97" s="7">
+        <f t="shared" si="1"/>
+        <v>163</v>
+      </c>
+      <c r="H97" s="7"/>
+      <c r="I97" s="7">
+        <f t="shared" si="0"/>
+        <v>90000000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D98" s="8"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G98" s="7">
+        <f t="shared" si="1"/>
+        <v>163</v>
+      </c>
+      <c r="H98" s="7"/>
+      <c r="I98" s="7">
+        <f t="shared" si="0"/>
+        <v>90000000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D99" s="8"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G99" s="7">
+        <f t="shared" si="1"/>
+        <v>164</v>
+      </c>
+      <c r="H99" s="7"/>
+      <c r="I99" s="7">
+        <f t="shared" si="0"/>
+        <v>95000000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D100" s="8"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G100" s="7">
+        <f t="shared" si="1"/>
+        <v>164</v>
+      </c>
+      <c r="H100" s="7"/>
+      <c r="I100" s="7">
+        <f t="shared" si="0"/>
+        <v>95000000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D101" s="8"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G101" s="7">
+        <f t="shared" si="1"/>
+        <v>165</v>
+      </c>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7">
+        <f t="shared" si="0"/>
+        <v>100000000</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B13">
@@ -2613,7 +3726,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B72 B73:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"等级,杀怪,战力,称号,强化,技能,升箱,boss"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2634,10 +3747,10 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:2">
